--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_synthesisRateGroup.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_synthesisRateGroup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" firstSheet="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="1"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_synthesisRateGroup" sheetId="4" r:id="rId1"/>
@@ -80,7 +80,7 @@
     <t>一代翅膀合成</t>
   </si>
   <si>
-    <t>1#5#1000|6#6#2000|7#7#3000|8#8#4000|9#9#5000|10#10#6000|11#11#7000|12#12#8000|13#13#9000</t>
+    <t>1#5#1000|6#6#1500|7#7#2000|8#8#2500|9#9#3000|10#10#4000|11#11#5000|12#12#6000|13#13#7000</t>
   </si>
   <si>
     <t>326012#1#10000#500</t>
@@ -135,13 +135,18 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -288,7 +293,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -297,6 +302,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -382,12 +399,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -608,76 +619,70 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
@@ -686,59 +691,65 @@
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -747,6 +758,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1059,7 +1076,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1231,7 +1248,27 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" ht="14" customHeight="1"/>
+    <row r="16" ht="14" customHeight="1" spans="1:5">
+      <c r="B16" s="3"/>
+    </row>
+    <row r="17" ht="15" spans="2:2">
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18" ht="15" spans="2:2">
+      <c r="B18" s="3"/>
+    </row>
+    <row r="19" ht="15" spans="2:2">
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" ht="15" spans="2:2">
+      <c r="B20" s="4"/>
+    </row>
+    <row r="21" ht="15" spans="2:2">
+      <c r="B21" s="3"/>
+    </row>
+    <row r="22" ht="15" spans="2:2">
+      <c r="B22" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
